--- a/Team-Data/2014-15/4-14-2014-15.xlsx
+++ b/Team-Data/2014-15/4-14-2014-15.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,7 +806,7 @@
         <v>5.6</v>
       </c>
       <c r="AD2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE2" t="n">
         <v>2</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>4-14-2014-15</t>
+          <t>2015-04-14</t>
         </is>
       </c>
     </row>
@@ -843,16 +910,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E3" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F3" t="n">
         <v>42</v>
       </c>
       <c r="G3" t="n">
-        <v>0.481</v>
+        <v>0.475</v>
       </c>
       <c r="H3" t="n">
         <v>48.5</v>
@@ -861,10 +928,10 @@
         <v>38.9</v>
       </c>
       <c r="J3" t="n">
-        <v>88</v>
+        <v>87.8</v>
       </c>
       <c r="K3" t="n">
-        <v>0.442</v>
+        <v>0.443</v>
       </c>
       <c r="L3" t="n">
         <v>8</v>
@@ -873,16 +940,16 @@
         <v>24.6</v>
       </c>
       <c r="N3" t="n">
-        <v>0.325</v>
+        <v>0.326</v>
       </c>
       <c r="O3" t="n">
-        <v>15.5</v>
+        <v>15.6</v>
       </c>
       <c r="P3" t="n">
-        <v>20.5</v>
+        <v>20.6</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.756</v>
+        <v>0.755</v>
       </c>
       <c r="R3" t="n">
         <v>11.1</v>
@@ -891,10 +958,10 @@
         <v>32.8</v>
       </c>
       <c r="T3" t="n">
-        <v>43.9</v>
+        <v>43.8</v>
       </c>
       <c r="U3" t="n">
-        <v>24.3</v>
+        <v>24.4</v>
       </c>
       <c r="V3" t="n">
         <v>13.8</v>
@@ -903,7 +970,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="X3" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="Y3" t="n">
         <v>5.3</v>
@@ -915,25 +982,25 @@
         <v>18.9</v>
       </c>
       <c r="AB3" t="n">
-        <v>101.3</v>
+        <v>101.4</v>
       </c>
       <c r="AC3" t="n">
         <v>0.1</v>
       </c>
       <c r="AD3" t="n">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="AE3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AF3" t="n">
         <v>16</v>
       </c>
       <c r="AG3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AH3" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AI3" t="n">
         <v>5</v>
@@ -942,7 +1009,7 @@
         <v>1</v>
       </c>
       <c r="AK3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AL3" t="n">
         <v>14</v>
@@ -960,10 +1027,10 @@
         <v>27</v>
       </c>
       <c r="AQ3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AR3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AS3" t="n">
         <v>11</v>
@@ -984,7 +1051,7 @@
         <v>30</v>
       </c>
       <c r="AY3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AZ3" t="n">
         <v>22</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>4-14-2014-15</t>
+          <t>2015-04-14</t>
         </is>
       </c>
     </row>
@@ -1103,10 +1170,10 @@
         <v>-3.1</v>
       </c>
       <c r="AD4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AF4" t="n">
         <v>20</v>
@@ -1115,7 +1182,7 @@
         <v>20</v>
       </c>
       <c r="AH4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI4" t="n">
         <v>18</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>4-14-2014-15</t>
+          <t>2015-04-14</t>
         </is>
       </c>
     </row>
@@ -1285,7 +1352,7 @@
         <v>-3.1</v>
       </c>
       <c r="AD5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE5" t="n">
         <v>22</v>
@@ -1297,7 +1364,7 @@
         <v>22</v>
       </c>
       <c r="AH5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AI5" t="n">
         <v>26</v>
@@ -1330,7 +1397,7 @@
         <v>25</v>
       </c>
       <c r="AS5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AT5" t="n">
         <v>10</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>4-14-2014-15</t>
+          <t>2015-04-14</t>
         </is>
       </c>
     </row>
@@ -1467,16 +1534,16 @@
         <v>3</v>
       </c>
       <c r="AD6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE6" t="n">
         <v>9</v>
       </c>
       <c r="AF6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AH6" t="n">
         <v>9</v>
@@ -1509,7 +1576,7 @@
         <v>3</v>
       </c>
       <c r="AR6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AS6" t="n">
         <v>7</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>4-14-2014-15</t>
+          <t>2015-04-14</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1716,7 @@
         <v>4.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE7" t="n">
         <v>7</v>
@@ -1661,7 +1728,7 @@
         <v>7</v>
       </c>
       <c r="AH7" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI7" t="n">
         <v>15</v>
@@ -1691,7 +1758,7 @@
         <v>17</v>
       </c>
       <c r="AR7" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AS7" t="n">
         <v>20</v>
@@ -1700,7 +1767,7 @@
         <v>18</v>
       </c>
       <c r="AU7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AV7" t="n">
         <v>17</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>4-14-2014-15</t>
+          <t>2015-04-14</t>
         </is>
       </c>
     </row>
@@ -1753,16 +1820,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E8" t="n">
         <v>49</v>
       </c>
       <c r="F8" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G8" t="n">
-        <v>0.613</v>
+        <v>0.605</v>
       </c>
       <c r="H8" t="n">
         <v>48.5</v>
@@ -1771,16 +1838,16 @@
         <v>39.7</v>
       </c>
       <c r="J8" t="n">
-        <v>85.90000000000001</v>
+        <v>85.8</v>
       </c>
       <c r="K8" t="n">
-        <v>0.462</v>
+        <v>0.463</v>
       </c>
       <c r="L8" t="n">
         <v>8.9</v>
       </c>
       <c r="M8" t="n">
-        <v>25.5</v>
+        <v>25.4</v>
       </c>
       <c r="N8" t="n">
         <v>0.351</v>
@@ -1789,25 +1856,25 @@
         <v>16.8</v>
       </c>
       <c r="P8" t="n">
-        <v>22.4</v>
+        <v>22.3</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.75</v>
+        <v>0.751</v>
       </c>
       <c r="R8" t="n">
-        <v>10.5</v>
+        <v>10.4</v>
       </c>
       <c r="S8" t="n">
-        <v>31.8</v>
+        <v>31.7</v>
       </c>
       <c r="T8" t="n">
-        <v>42.2</v>
+        <v>42.1</v>
       </c>
       <c r="U8" t="n">
         <v>22.6</v>
       </c>
       <c r="V8" t="n">
-        <v>13</v>
+        <v>12.9</v>
       </c>
       <c r="W8" t="n">
         <v>8.1</v>
@@ -1822,16 +1889,16 @@
         <v>20.1</v>
       </c>
       <c r="AA8" t="n">
-        <v>22.2</v>
+        <v>22.1</v>
       </c>
       <c r="AB8" t="n">
-        <v>105.2</v>
+        <v>105.1</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="AD8" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="AE8" t="n">
         <v>9</v>
@@ -1843,13 +1910,13 @@
         <v>9</v>
       </c>
       <c r="AH8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AI8" t="n">
         <v>2</v>
       </c>
       <c r="AJ8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AK8" t="n">
         <v>6</v>
@@ -1864,10 +1931,10 @@
         <v>13</v>
       </c>
       <c r="AO8" t="n">
+        <v>16</v>
+      </c>
+      <c r="AP8" t="n">
         <v>17</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>16</v>
       </c>
       <c r="AQ8" t="n">
         <v>18</v>
@@ -1876,7 +1943,7 @@
         <v>19</v>
       </c>
       <c r="AS8" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AT8" t="n">
         <v>23</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>4-14-2014-15</t>
+          <t>2015-04-14</t>
         </is>
       </c>
     </row>
@@ -2013,7 +2080,7 @@
         <v>-3.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE9" t="n">
         <v>24</v>
@@ -2058,7 +2125,7 @@
         <v>3</v>
       </c>
       <c r="AS9" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AT9" t="n">
         <v>7</v>
@@ -2070,10 +2137,10 @@
         <v>15</v>
       </c>
       <c r="AW9" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AX9" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AY9" t="n">
         <v>29</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>4-14-2014-15</t>
+          <t>2015-04-14</t>
         </is>
       </c>
     </row>
@@ -2195,7 +2262,7 @@
         <v>-1.3</v>
       </c>
       <c r="AD10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE10" t="n">
         <v>23</v>
@@ -2207,7 +2274,7 @@
         <v>23</v>
       </c>
       <c r="AH10" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AI10" t="n">
         <v>20</v>
@@ -2231,7 +2298,7 @@
         <v>26</v>
       </c>
       <c r="AP10" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AQ10" t="n">
         <v>29</v>
@@ -2243,7 +2310,7 @@
         <v>16</v>
       </c>
       <c r="AT10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AU10" t="n">
         <v>16</v>
@@ -2264,7 +2331,7 @@
         <v>7</v>
       </c>
       <c r="BA10" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BB10" t="n">
         <v>20</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>4-14-2014-15</t>
+          <t>2015-04-14</t>
         </is>
       </c>
     </row>
@@ -2377,7 +2444,7 @@
         <v>10.1</v>
       </c>
       <c r="AD11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE11" t="n">
         <v>1</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>4-14-2014-15</t>
+          <t>2015-04-14</t>
         </is>
       </c>
     </row>
@@ -2481,25 +2548,25 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E12" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F12" t="n">
         <v>26</v>
       </c>
       <c r="G12" t="n">
-        <v>0.675</v>
+        <v>0.679</v>
       </c>
       <c r="H12" t="n">
         <v>48.3</v>
       </c>
       <c r="I12" t="n">
-        <v>37</v>
+        <v>36.9</v>
       </c>
       <c r="J12" t="n">
-        <v>83.5</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="K12" t="n">
         <v>0.443</v>
@@ -2508,16 +2575,16 @@
         <v>11.4</v>
       </c>
       <c r="M12" t="n">
-        <v>32.8</v>
+        <v>32.7</v>
       </c>
       <c r="N12" t="n">
         <v>0.347</v>
       </c>
       <c r="O12" t="n">
-        <v>18.4</v>
+        <v>18.5</v>
       </c>
       <c r="P12" t="n">
-        <v>25.6</v>
+        <v>25.9</v>
       </c>
       <c r="Q12" t="n">
         <v>0.716</v>
@@ -2535,7 +2602,7 @@
         <v>22.1</v>
       </c>
       <c r="V12" t="n">
-        <v>16.7</v>
+        <v>16.6</v>
       </c>
       <c r="W12" t="n">
         <v>9.5</v>
@@ -2544,31 +2611,31 @@
         <v>4.9</v>
       </c>
       <c r="Y12" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="Z12" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="AA12" t="n">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="AB12" t="n">
-        <v>103.7</v>
+        <v>103.8</v>
       </c>
       <c r="AC12" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE12" t="n">
         <v>3</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>25</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>4</v>
       </c>
       <c r="AF12" t="n">
         <v>3</v>
       </c>
       <c r="AG12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AH12" t="n">
         <v>20</v>
@@ -2580,7 +2647,7 @@
         <v>12</v>
       </c>
       <c r="AK12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AL12" t="n">
         <v>1</v>
@@ -2589,22 +2656,22 @@
         <v>1</v>
       </c>
       <c r="AN12" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AO12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AP12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AQ12" t="n">
         <v>27</v>
       </c>
       <c r="AR12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AS12" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AT12" t="n">
         <v>15</v>
@@ -2622,7 +2689,7 @@
         <v>11</v>
       </c>
       <c r="AY12" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AZ12" t="n">
         <v>27</v>
@@ -2634,7 +2701,7 @@
         <v>5</v>
       </c>
       <c r="BC12" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BD12" t="n">
         <v>10</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>4-14-2014-15</t>
+          <t>2015-04-14</t>
         </is>
       </c>
     </row>
@@ -2663,55 +2730,55 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E13" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F13" t="n">
         <v>43</v>
       </c>
       <c r="G13" t="n">
-        <v>0.469</v>
+        <v>0.463</v>
       </c>
       <c r="H13" t="n">
-        <v>48.4</v>
+        <v>48.3</v>
       </c>
       <c r="I13" t="n">
         <v>36.6</v>
       </c>
       <c r="J13" t="n">
-        <v>83.3</v>
+        <v>83</v>
       </c>
       <c r="K13" t="n">
-        <v>0.44</v>
+        <v>0.441</v>
       </c>
       <c r="L13" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="M13" t="n">
-        <v>21.2</v>
+        <v>21.1</v>
       </c>
       <c r="N13" t="n">
-        <v>0.352</v>
+        <v>0.353</v>
       </c>
       <c r="O13" t="n">
-        <v>16.8</v>
+        <v>16.9</v>
       </c>
       <c r="P13" t="n">
-        <v>22.2</v>
+        <v>22.3</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.756</v>
+        <v>0.757</v>
       </c>
       <c r="R13" t="n">
         <v>10.4</v>
       </c>
       <c r="S13" t="n">
-        <v>34.6</v>
+        <v>34.5</v>
       </c>
       <c r="T13" t="n">
-        <v>45</v>
+        <v>44.8</v>
       </c>
       <c r="U13" t="n">
         <v>21.5</v>
@@ -2720,13 +2787,13 @@
         <v>14</v>
       </c>
       <c r="W13" t="n">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="X13" t="n">
         <v>4.5</v>
       </c>
       <c r="Y13" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="Z13" t="n">
         <v>21.2</v>
@@ -2741,25 +2808,25 @@
         <v>0.4</v>
       </c>
       <c r="AD13" t="n">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="AE13" t="n">
+        <v>19</v>
+      </c>
+      <c r="AF13" t="n">
         <v>18</v>
       </c>
-      <c r="AF13" t="n">
-        <v>17</v>
-      </c>
       <c r="AG13" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AH13" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="AI13" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AJ13" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AK13" t="n">
         <v>23</v>
@@ -2771,7 +2838,7 @@
         <v>18</v>
       </c>
       <c r="AN13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AO13" t="n">
         <v>15</v>
@@ -2780,16 +2847,16 @@
         <v>18</v>
       </c>
       <c r="AQ13" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AR13" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AS13" t="n">
         <v>3</v>
       </c>
       <c r="AT13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AU13" t="n">
         <v>18</v>
@@ -2801,7 +2868,7 @@
         <v>29</v>
       </c>
       <c r="AX13" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AY13" t="n">
         <v>14</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>4-14-2014-15</t>
+          <t>2015-04-14</t>
         </is>
       </c>
     </row>
@@ -2845,49 +2912,49 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E14" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F14" t="n">
         <v>26</v>
       </c>
       <c r="G14" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.679</v>
       </c>
       <c r="H14" t="n">
         <v>48.1</v>
       </c>
       <c r="I14" t="n">
-        <v>39.4</v>
+        <v>39.3</v>
       </c>
       <c r="J14" t="n">
-        <v>83.3</v>
+        <v>83.2</v>
       </c>
       <c r="K14" t="n">
-        <v>0.473</v>
+        <v>0.472</v>
       </c>
       <c r="L14" t="n">
-        <v>10.1</v>
+        <v>10</v>
       </c>
       <c r="M14" t="n">
-        <v>26.9</v>
+        <v>26.7</v>
       </c>
       <c r="N14" t="n">
-        <v>0.376</v>
+        <v>0.375</v>
       </c>
       <c r="O14" t="n">
-        <v>17.9</v>
+        <v>18</v>
       </c>
       <c r="P14" t="n">
-        <v>25.2</v>
+        <v>25.3</v>
       </c>
       <c r="Q14" t="n">
         <v>0.71</v>
       </c>
       <c r="R14" t="n">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="S14" t="n">
         <v>33.1</v>
@@ -2911,16 +2978,16 @@
         <v>3</v>
       </c>
       <c r="Z14" t="n">
-        <v>21.3</v>
+        <v>21.4</v>
       </c>
       <c r="AA14" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="AB14" t="n">
         <v>106.7</v>
       </c>
       <c r="AC14" t="n">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="AD14" t="n">
         <v>1</v>
@@ -2935,7 +3002,7 @@
         <v>3</v>
       </c>
       <c r="AH14" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AI14" t="n">
         <v>3</v>
@@ -2980,7 +3047,7 @@
         <v>2</v>
       </c>
       <c r="AW14" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AX14" t="n">
         <v>9</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>4-14-2014-15</t>
+          <t>2015-04-14</t>
         </is>
       </c>
     </row>
@@ -3027,58 +3094,58 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E15" t="n">
         <v>21</v>
       </c>
       <c r="F15" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G15" t="n">
-        <v>0.263</v>
+        <v>0.259</v>
       </c>
       <c r="H15" t="n">
         <v>48.6</v>
       </c>
       <c r="I15" t="n">
-        <v>37.4</v>
+        <v>37.3</v>
       </c>
       <c r="J15" t="n">
-        <v>85.59999999999999</v>
+        <v>85.5</v>
       </c>
       <c r="K15" t="n">
-        <v>0.437</v>
+        <v>0.436</v>
       </c>
       <c r="L15" t="n">
         <v>6.5</v>
       </c>
       <c r="M15" t="n">
-        <v>18.9</v>
+        <v>18.8</v>
       </c>
       <c r="N15" t="n">
         <v>0.345</v>
       </c>
       <c r="O15" t="n">
-        <v>17.3</v>
+        <v>17.4</v>
       </c>
       <c r="P15" t="n">
-        <v>23.4</v>
+        <v>23.6</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.739</v>
+        <v>0.74</v>
       </c>
       <c r="R15" t="n">
         <v>11.6</v>
       </c>
       <c r="S15" t="n">
-        <v>32.4</v>
+        <v>32.3</v>
       </c>
       <c r="T15" t="n">
-        <v>44</v>
+        <v>43.9</v>
       </c>
       <c r="U15" t="n">
-        <v>21</v>
+        <v>20.9</v>
       </c>
       <c r="V15" t="n">
         <v>13.2</v>
@@ -3090,22 +3157,22 @@
         <v>4.4</v>
       </c>
       <c r="Y15" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="Z15" t="n">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="AA15" t="n">
-        <v>19.3</v>
+        <v>19.4</v>
       </c>
       <c r="AB15" t="n">
-        <v>98.59999999999999</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="AC15" t="n">
-        <v>-6.5</v>
+        <v>-6.6</v>
       </c>
       <c r="AD15" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="AE15" t="n">
         <v>27</v>
@@ -3150,7 +3217,7 @@
         <v>8</v>
       </c>
       <c r="AS15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AT15" t="n">
         <v>12</v>
@@ -3174,10 +3241,10 @@
         <v>20</v>
       </c>
       <c r="BA15" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BB15" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BC15" t="n">
         <v>27</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>4-14-2014-15</t>
+          <t>2015-04-14</t>
         </is>
       </c>
     </row>
@@ -3287,10 +3354,10 @@
         <v>3.1</v>
       </c>
       <c r="AD16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE16" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AF16" t="n">
         <v>6</v>
@@ -3299,13 +3366,13 @@
         <v>6</v>
       </c>
       <c r="AH16" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AI16" t="n">
         <v>13</v>
       </c>
       <c r="AJ16" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AK16" t="n">
         <v>9</v>
@@ -3317,7 +3384,7 @@
         <v>29</v>
       </c>
       <c r="AN16" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AO16" t="n">
         <v>10</v>
@@ -3329,7 +3396,7 @@
         <v>7</v>
       </c>
       <c r="AR16" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AS16" t="n">
         <v>15</v>
@@ -3341,7 +3408,7 @@
         <v>14</v>
       </c>
       <c r="AV16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AW16" t="n">
         <v>7</v>
@@ -3362,7 +3429,7 @@
         <v>19</v>
       </c>
       <c r="BC16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BD16" t="n">
         <v>10</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>4-14-2014-15</t>
+          <t>2015-04-14</t>
         </is>
       </c>
     </row>
@@ -3469,7 +3536,7 @@
         <v>-2.7</v>
       </c>
       <c r="AD17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE17" t="n">
         <v>21</v>
@@ -3526,7 +3593,7 @@
         <v>21</v>
       </c>
       <c r="AW17" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AX17" t="n">
         <v>16</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>4-14-2014-15</t>
+          <t>2015-04-14</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3718,7 @@
         <v>0.5</v>
       </c>
       <c r="AD18" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE18" t="n">
         <v>15</v>
@@ -3663,10 +3730,10 @@
         <v>15</v>
       </c>
       <c r="AH18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI18" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AJ18" t="n">
         <v>26</v>
@@ -3690,7 +3757,7 @@
         <v>25</v>
       </c>
       <c r="AQ18" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AR18" t="n">
         <v>17</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>4-14-2014-15</t>
+          <t>2015-04-14</t>
         </is>
       </c>
     </row>
@@ -3833,7 +3900,7 @@
         <v>-8.6</v>
       </c>
       <c r="AD19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE19" t="n">
         <v>30</v>
@@ -3845,13 +3912,13 @@
         <v>30</v>
       </c>
       <c r="AH19" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI19" t="n">
         <v>25</v>
       </c>
       <c r="AJ19" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AK19" t="n">
         <v>24</v>
@@ -3869,7 +3936,7 @@
         <v>2</v>
       </c>
       <c r="AP19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ19" t="n">
         <v>6</v>
@@ -3890,7 +3957,7 @@
         <v>23</v>
       </c>
       <c r="AW19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AX19" t="n">
         <v>27</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>4-14-2014-15</t>
+          <t>2015-04-14</t>
         </is>
       </c>
     </row>
@@ -3937,25 +4004,25 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E20" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F20" t="n">
         <v>37</v>
       </c>
       <c r="G20" t="n">
-        <v>0.538</v>
+        <v>0.543</v>
       </c>
       <c r="H20" t="n">
-        <v>48.3</v>
+        <v>48.2</v>
       </c>
       <c r="I20" t="n">
         <v>37.8</v>
       </c>
       <c r="J20" t="n">
-        <v>82.59999999999999</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="K20" t="n">
         <v>0.457</v>
@@ -3964,40 +4031,40 @@
         <v>7.2</v>
       </c>
       <c r="M20" t="n">
-        <v>19.5</v>
+        <v>19.4</v>
       </c>
       <c r="N20" t="n">
-        <v>0.371</v>
+        <v>0.369</v>
       </c>
       <c r="O20" t="n">
         <v>16.4</v>
       </c>
       <c r="P20" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.757</v>
+        <v>0.752</v>
       </c>
       <c r="R20" t="n">
-        <v>11.4</v>
+        <v>11.5</v>
       </c>
       <c r="S20" t="n">
         <v>32</v>
       </c>
       <c r="T20" t="n">
-        <v>43.3</v>
+        <v>43.6</v>
       </c>
       <c r="U20" t="n">
         <v>22</v>
       </c>
       <c r="V20" t="n">
-        <v>13.4</v>
+        <v>13.3</v>
       </c>
       <c r="W20" t="n">
         <v>6.7</v>
       </c>
       <c r="X20" t="n">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="Y20" t="n">
         <v>5.8</v>
@@ -4006,25 +4073,25 @@
         <v>18.7</v>
       </c>
       <c r="AA20" t="n">
-        <v>18.6</v>
+        <v>18.7</v>
       </c>
       <c r="AB20" t="n">
         <v>99.2</v>
       </c>
       <c r="AC20" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="AD20" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="AE20" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AF20" t="n">
         <v>13</v>
       </c>
       <c r="AG20" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AH20" t="n">
         <v>23</v>
@@ -4033,7 +4100,7 @@
         <v>12</v>
       </c>
       <c r="AJ20" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AK20" t="n">
         <v>10</v>
@@ -4048,16 +4115,16 @@
         <v>4</v>
       </c>
       <c r="AO20" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AP20" t="n">
         <v>20</v>
       </c>
       <c r="AQ20" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AR20" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AS20" t="n">
         <v>18</v>
@@ -4066,13 +4133,13 @@
         <v>16</v>
       </c>
       <c r="AU20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AV20" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW20" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AX20" t="n">
         <v>1</v>
@@ -4090,7 +4157,7 @@
         <v>16</v>
       </c>
       <c r="BC20" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BD20" t="n">
         <v>10</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>4-14-2014-15</t>
+          <t>2015-04-14</t>
         </is>
       </c>
     </row>
@@ -4197,7 +4264,7 @@
         <v>-9.199999999999999</v>
       </c>
       <c r="AD21" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE21" t="n">
         <v>29</v>
@@ -4209,7 +4276,7 @@
         <v>29</v>
       </c>
       <c r="AH21" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AI21" t="n">
         <v>28</v>
@@ -4227,7 +4294,7 @@
         <v>21</v>
       </c>
       <c r="AN21" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AO21" t="n">
         <v>29</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>4-14-2014-15</t>
+          <t>2015-04-14</t>
         </is>
       </c>
     </row>
@@ -4379,7 +4446,7 @@
         <v>1.9</v>
       </c>
       <c r="AD22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE22" t="n">
         <v>13</v>
@@ -4391,7 +4458,7 @@
         <v>13</v>
       </c>
       <c r="AH22" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AI22" t="n">
         <v>8</v>
@@ -4406,7 +4473,7 @@
         <v>16</v>
       </c>
       <c r="AM22" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AN22" t="n">
         <v>23</v>
@@ -4418,7 +4485,7 @@
         <v>7</v>
       </c>
       <c r="AQ22" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AR22" t="n">
         <v>2</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>4-14-2014-15</t>
+          <t>2015-04-14</t>
         </is>
       </c>
     </row>
@@ -4483,22 +4550,22 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E23" t="n">
         <v>25</v>
       </c>
       <c r="F23" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G23" t="n">
-        <v>0.313</v>
+        <v>0.309</v>
       </c>
       <c r="H23" t="n">
         <v>48.2</v>
       </c>
       <c r="I23" t="n">
-        <v>37.6</v>
+        <v>37.5</v>
       </c>
       <c r="J23" t="n">
         <v>82.90000000000001</v>
@@ -4510,7 +4577,7 @@
         <v>6.8</v>
       </c>
       <c r="M23" t="n">
-        <v>19.6</v>
+        <v>19.5</v>
       </c>
       <c r="N23" t="n">
         <v>0.347</v>
@@ -4519,7 +4586,7 @@
         <v>14</v>
       </c>
       <c r="P23" t="n">
-        <v>19.1</v>
+        <v>19.2</v>
       </c>
       <c r="Q23" t="n">
         <v>0.732</v>
@@ -4528,25 +4595,25 @@
         <v>10</v>
       </c>
       <c r="S23" t="n">
-        <v>31.7</v>
+        <v>31.8</v>
       </c>
       <c r="T23" t="n">
-        <v>41.6</v>
+        <v>41.8</v>
       </c>
       <c r="U23" t="n">
         <v>20.7</v>
       </c>
       <c r="V23" t="n">
-        <v>14.8</v>
+        <v>14.9</v>
       </c>
       <c r="W23" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="X23" t="n">
         <v>3.8</v>
       </c>
       <c r="Y23" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="Z23" t="n">
         <v>20.9</v>
@@ -4555,13 +4622,13 @@
         <v>18</v>
       </c>
       <c r="AB23" t="n">
-        <v>95.90000000000001</v>
+        <v>95.8</v>
       </c>
       <c r="AC23" t="n">
-        <v>-5.5</v>
+        <v>-5.6</v>
       </c>
       <c r="AD23" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="AE23" t="n">
         <v>26</v>
@@ -4576,7 +4643,7 @@
         <v>24</v>
       </c>
       <c r="AI23" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AJ23" t="n">
         <v>19</v>
@@ -4603,16 +4670,16 @@
         <v>25</v>
       </c>
       <c r="AR23" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AS23" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AT23" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AU23" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AV23" t="n">
         <v>22</v>
@@ -4624,10 +4691,10 @@
         <v>29</v>
       </c>
       <c r="AY23" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AZ23" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BA23" t="n">
         <v>30</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>4-14-2014-15</t>
+          <t>2015-04-14</t>
         </is>
       </c>
     </row>
@@ -4743,7 +4810,7 @@
         <v>-9</v>
       </c>
       <c r="AD24" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE24" t="n">
         <v>28</v>
@@ -4755,19 +4822,19 @@
         <v>28</v>
       </c>
       <c r="AH24" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI24" t="n">
         <v>30</v>
       </c>
       <c r="AJ24" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AK24" t="n">
         <v>30</v>
       </c>
       <c r="AL24" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AM24" t="n">
         <v>6</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>4-14-2014-15</t>
+          <t>2015-04-14</t>
         </is>
       </c>
     </row>
@@ -4847,16 +4914,16 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E25" t="n">
         <v>39</v>
       </c>
       <c r="F25" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G25" t="n">
-        <v>0.476</v>
+        <v>0.481</v>
       </c>
       <c r="H25" t="n">
         <v>48.5</v>
@@ -4865,10 +4932,10 @@
         <v>38.8</v>
       </c>
       <c r="J25" t="n">
-        <v>85.8</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="K25" t="n">
-        <v>0.452</v>
+        <v>0.451</v>
       </c>
       <c r="L25" t="n">
         <v>8.5</v>
@@ -4877,22 +4944,22 @@
         <v>25</v>
       </c>
       <c r="N25" t="n">
-        <v>0.341</v>
+        <v>0.34</v>
       </c>
       <c r="O25" t="n">
         <v>16.4</v>
       </c>
       <c r="P25" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.76</v>
+        <v>0.762</v>
       </c>
       <c r="R25" t="n">
         <v>10.9</v>
       </c>
       <c r="S25" t="n">
-        <v>32.2</v>
+        <v>32.3</v>
       </c>
       <c r="T25" t="n">
         <v>43.2</v>
@@ -4922,7 +4989,7 @@
         <v>102.4</v>
       </c>
       <c r="AC25" t="n">
-        <v>-0.9</v>
+        <v>-0.8</v>
       </c>
       <c r="AD25" t="n">
         <v>1</v>
@@ -4931,19 +4998,19 @@
         <v>16</v>
       </c>
       <c r="AF25" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AG25" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AH25" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AI25" t="n">
         <v>6</v>
       </c>
       <c r="AJ25" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AK25" t="n">
         <v>15</v>
@@ -4955,13 +5022,13 @@
         <v>10</v>
       </c>
       <c r="AN25" t="n">
+        <v>22</v>
+      </c>
+      <c r="AO25" t="n">
         <v>20</v>
       </c>
-      <c r="AO25" t="n">
+      <c r="AP25" t="n">
         <v>21</v>
-      </c>
-      <c r="AP25" t="n">
-        <v>22</v>
       </c>
       <c r="AQ25" t="n">
         <v>11</v>
@@ -4976,7 +5043,7 @@
         <v>17</v>
       </c>
       <c r="AU25" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AV25" t="n">
         <v>25</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>4-14-2014-15</t>
+          <t>2015-04-14</t>
         </is>
       </c>
     </row>
@@ -5107,7 +5174,7 @@
         <v>4.5</v>
       </c>
       <c r="AD26" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE26" t="n">
         <v>8</v>
@@ -5119,7 +5186,7 @@
         <v>8</v>
       </c>
       <c r="AH26" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AI26" t="n">
         <v>7</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>4-14-2014-15</t>
+          <t>2015-04-14</t>
         </is>
       </c>
     </row>
@@ -5289,7 +5356,7 @@
         <v>-4</v>
       </c>
       <c r="AD27" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE27" t="n">
         <v>25</v>
@@ -5301,10 +5368,10 @@
         <v>25</v>
       </c>
       <c r="AH27" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AI27" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AJ27" t="n">
         <v>28</v>
@@ -5319,7 +5386,7 @@
         <v>28</v>
       </c>
       <c r="AN27" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AO27" t="n">
         <v>1</v>
@@ -5340,13 +5407,13 @@
         <v>9</v>
       </c>
       <c r="AU27" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AV27" t="n">
         <v>27</v>
       </c>
       <c r="AW27" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AX27" t="n">
         <v>28</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>4-14-2014-15</t>
+          <t>2015-04-14</t>
         </is>
       </c>
     </row>
@@ -5393,43 +5460,43 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E28" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F28" t="n">
         <v>26</v>
       </c>
       <c r="G28" t="n">
-        <v>0.675</v>
+        <v>0.679</v>
       </c>
       <c r="H28" t="n">
         <v>48.7</v>
       </c>
       <c r="I28" t="n">
-        <v>39.1</v>
+        <v>39</v>
       </c>
       <c r="J28" t="n">
-        <v>83.8</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="K28" t="n">
-        <v>0.466</v>
+        <v>0.467</v>
       </c>
       <c r="L28" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="M28" t="n">
-        <v>22.6</v>
+        <v>22.7</v>
       </c>
       <c r="N28" t="n">
-        <v>0.365</v>
+        <v>0.367</v>
       </c>
       <c r="O28" t="n">
         <v>16.8</v>
       </c>
       <c r="P28" t="n">
-        <v>21.6</v>
+        <v>21.5</v>
       </c>
       <c r="Q28" t="n">
         <v>0.78</v>
@@ -5438,22 +5505,22 @@
         <v>9.9</v>
       </c>
       <c r="S28" t="n">
-        <v>33.9</v>
+        <v>33.8</v>
       </c>
       <c r="T28" t="n">
-        <v>43.8</v>
+        <v>43.7</v>
       </c>
       <c r="U28" t="n">
         <v>24.3</v>
       </c>
       <c r="V28" t="n">
-        <v>13.9</v>
+        <v>14</v>
       </c>
       <c r="W28" t="n">
         <v>8.1</v>
       </c>
       <c r="X28" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="Y28" t="n">
         <v>4.4</v>
@@ -5468,19 +5535,19 @@
         <v>103.2</v>
       </c>
       <c r="AC28" t="n">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="AD28" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="AE28" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AF28" t="n">
         <v>3</v>
       </c>
       <c r="AG28" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AH28" t="n">
         <v>1</v>
@@ -5498,16 +5565,16 @@
         <v>12</v>
       </c>
       <c r="AM28" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AN28" t="n">
         <v>5</v>
       </c>
       <c r="AO28" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AP28" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AQ28" t="n">
         <v>4</v>
@@ -5528,7 +5595,7 @@
         <v>13</v>
       </c>
       <c r="AW28" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AX28" t="n">
         <v>8</v>
@@ -5540,7 +5607,7 @@
         <v>8</v>
       </c>
       <c r="BA28" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BB28" t="n">
         <v>7</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>4-14-2014-15</t>
+          <t>2015-04-14</t>
         </is>
       </c>
     </row>
@@ -5575,16 +5642,16 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E29" t="n">
         <v>48</v>
       </c>
       <c r="F29" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G29" t="n">
-        <v>0.593</v>
+        <v>0.6</v>
       </c>
       <c r="H29" t="n">
         <v>48.4</v>
@@ -5608,19 +5675,19 @@
         <v>0.352</v>
       </c>
       <c r="O29" t="n">
-        <v>19.5</v>
+        <v>19.6</v>
       </c>
       <c r="P29" t="n">
-        <v>24.8</v>
+        <v>24.9</v>
       </c>
       <c r="Q29" t="n">
         <v>0.787</v>
       </c>
       <c r="R29" t="n">
-        <v>10.8</v>
+        <v>10.9</v>
       </c>
       <c r="S29" t="n">
-        <v>30.9</v>
+        <v>30.8</v>
       </c>
       <c r="T29" t="n">
         <v>41.7</v>
@@ -5629,37 +5696,37 @@
         <v>20.7</v>
       </c>
       <c r="V29" t="n">
-        <v>12.9</v>
+        <v>12.8</v>
       </c>
       <c r="W29" t="n">
         <v>7.5</v>
       </c>
       <c r="X29" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="Y29" t="n">
         <v>5.1</v>
       </c>
       <c r="Z29" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="AA29" t="n">
         <v>20.5</v>
       </c>
       <c r="AB29" t="n">
-        <v>104.1</v>
+        <v>104.3</v>
       </c>
       <c r="AC29" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="AD29" t="n">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="AE29" t="n">
         <v>11</v>
       </c>
       <c r="AF29" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AG29" t="n">
         <v>11</v>
@@ -5683,7 +5750,7 @@
         <v>9</v>
       </c>
       <c r="AN29" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AO29" t="n">
         <v>4</v>
@@ -5701,10 +5768,10 @@
         <v>27</v>
       </c>
       <c r="AT29" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AU29" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AV29" t="n">
         <v>3</v>
@@ -5728,7 +5795,7 @@
         <v>4</v>
       </c>
       <c r="BC29" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BD29" t="n">
         <v>10</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>4-14-2014-15</t>
+          <t>2015-04-14</t>
         </is>
       </c>
     </row>
@@ -5835,13 +5902,13 @@
         <v>0.5</v>
       </c>
       <c r="AD30" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE30" t="n">
+        <v>17</v>
+      </c>
+      <c r="AF30" t="n">
         <v>18</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>17</v>
       </c>
       <c r="AG30" t="n">
         <v>18</v>
@@ -5910,7 +5977,7 @@
         <v>26</v>
       </c>
       <c r="BC30" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BD30" t="n">
         <v>10</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>4-14-2014-15</t>
+          <t>2015-04-14</t>
         </is>
       </c>
     </row>
@@ -5939,61 +6006,61 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E31" t="n">
         <v>46</v>
       </c>
       <c r="F31" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G31" t="n">
-        <v>0.5679999999999999</v>
+        <v>0.575</v>
       </c>
       <c r="H31" t="n">
-        <v>48.6</v>
+        <v>48.5</v>
       </c>
       <c r="I31" t="n">
-        <v>38.2</v>
+        <v>38.3</v>
       </c>
       <c r="J31" t="n">
-        <v>82.59999999999999</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="K31" t="n">
-        <v>0.463</v>
+        <v>0.464</v>
       </c>
       <c r="L31" t="n">
         <v>6</v>
       </c>
       <c r="M31" t="n">
-        <v>16.8</v>
+        <v>16.7</v>
       </c>
       <c r="N31" t="n">
-        <v>0.36</v>
+        <v>0.361</v>
       </c>
       <c r="O31" t="n">
         <v>15.9</v>
       </c>
       <c r="P31" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.742</v>
+        <v>0.741</v>
       </c>
       <c r="R31" t="n">
-        <v>10.5</v>
+        <v>10.4</v>
       </c>
       <c r="S31" t="n">
-        <v>34.1</v>
+        <v>34</v>
       </c>
       <c r="T31" t="n">
-        <v>44.6</v>
+        <v>44.4</v>
       </c>
       <c r="U31" t="n">
         <v>24</v>
       </c>
       <c r="V31" t="n">
-        <v>15</v>
+        <v>15.1</v>
       </c>
       <c r="W31" t="n">
         <v>7.3</v>
@@ -6002,7 +6069,7 @@
         <v>4.6</v>
       </c>
       <c r="Y31" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="Z31" t="n">
         <v>20.9</v>
@@ -6011,13 +6078,13 @@
         <v>19.7</v>
       </c>
       <c r="AB31" t="n">
-        <v>98.40000000000001</v>
+        <v>98.5</v>
       </c>
       <c r="AC31" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="AD31" t="n">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="AE31" t="n">
         <v>12</v>
@@ -6029,13 +6096,13 @@
         <v>12</v>
       </c>
       <c r="AH31" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AI31" t="n">
         <v>9</v>
       </c>
       <c r="AJ31" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AK31" t="n">
         <v>5</v>
@@ -6053,7 +6120,7 @@
         <v>24</v>
       </c>
       <c r="AP31" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AQ31" t="n">
         <v>21</v>
@@ -6062,7 +6129,7 @@
         <v>20</v>
       </c>
       <c r="AS31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AT31" t="n">
         <v>8</v>
@@ -6083,13 +6150,13 @@
         <v>6</v>
       </c>
       <c r="AZ31" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BA31" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BB31" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BC31" t="n">
         <v>13</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>4-14-2014-15</t>
+          <t>2015-04-14</t>
         </is>
       </c>
     </row>
